--- a/experiment/ELAN_bestx4/Test/results_table.xlsx
+++ b/experiment/ELAN_bestx4/Test/results_table.xlsx
@@ -570,38 +570,38 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>32.206/
-0.8934</t>
+          <t>32.279/
+0.8943</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>28.622/
-0.7818</t>
+          <t>28.684/
+0.7830</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>27.612/
-0.7379</t>
+          <t>27.638/
+0.7388</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>26.198/
-0.7890</t>
+          <t>26.265/
+0.7914</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>30.588/
-0.9080</t>
+          <t>30.678/
+0.9094</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>29.045/
-0.8220</t>
+          <t>29.109/
+0.8234</t>
         </is>
       </c>
     </row>
